--- a/data/vzor_cenik_zetta90.xlsx
+++ b/data/vzor_cenik_zetta90.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="32760" yWindow="32760" windowWidth="18030" windowHeight="5625"/>
+    <workbookView windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="venkovní žaluzie" sheetId="3" r:id="rId1"/>
@@ -155,7 +155,7 @@
     <t>Montáž + doprava</t>
   </si>
   <si>
-    <t xml:space="preserve">Doprava </t>
+    <t>Doprava (1x zaměření 1x montáž)</t>
   </si>
   <si>
     <t xml:space="preserve">Montáž </t>
@@ -221,13 +221,11 @@
     <font>
       <sz val="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -235,7 +233,6 @@
       <sz val="10"/>
       <color indexed="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -243,28 +240,24 @@
       <sz val="9"/>
       <color indexed="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -277,7 +270,6 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -296,7 +288,6 @@
       <b/>
       <sz val="10"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -304,14 +295,12 @@
       <sz val="11"/>
       <color rgb="FF30A9C6"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -319,7 +308,6 @@
       <sz val="11"/>
       <color rgb="FF005F8E"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -333,13 +321,11 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -360,14 +346,12 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <i/>
       <sz val="8"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -375,14 +359,12 @@
       <i/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -390,7 +372,6 @@
       <i/>
       <sz val="10"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -398,53 +379,45 @@
       <i/>
       <sz val="7"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -483,7 +456,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -492,7 +464,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="Cambria"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="major"/>
     </font>
@@ -501,7 +472,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -510,7 +480,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -519,7 +488,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -528,7 +496,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -536,7 +503,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -545,7 +511,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -554,7 +519,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -563,7 +527,6 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -571,7 +534,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -580,7 +542,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -588,7 +549,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -596,7 +556,6 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -604,7 +563,6 @@
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -612,7 +570,6 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -620,7 +577,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
